--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-21_proses_dogrulama_gecerli_kilma_ve_yeterlilik_sonuc_rapo.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-21_proses_dogrulama_gecerli_kilma_ve_yeterlilik_sonuc_rapo.xlsx
@@ -1116,7 +1116,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-21&amp;C&amp;"Arial,Regular"&amp;11Proses Doğrulama, Geçerli Kılma ve Yeterlilik Sonuç Raporu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kapasite hesabında planlı süre ve duruş kapsamı düzeltildi; yeniden işlem çift sayımı önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d3a525d404d4932"/>
   <x:tableParts count="1">
@@ -1547,7 +1548,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-21&amp;C&amp;"Arial,Regular"&amp;11Proses Doğrulama, Geçerli Kılma ve Yeterlilik Sonuç Raporu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kapasite hesabında planlı süre ve duruş kapsamı düzeltildi; yeniden işlem çift sayımı önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde0b5a1d271c476c"/>
   <x:tableParts count="1">
@@ -1975,7 +1977,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-21&amp;C&amp;"Arial,Regular"&amp;11Proses Doğrulama, Geçerli Kılma ve Yeterlilik Sonuç Raporu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kapasite hesabında planlı süre ve duruş kapsamı düzeltildi; yeniden işlem çift sayımı önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8252a3c656547ab"/>
   <x:tableParts count="1">
@@ -2335,7 +2338,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-21&amp;C&amp;"Arial,Regular"&amp;11Proses Doğrulama, Geçerli Kılma ve Yeterlilik Sonuç Raporu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kapasite hesabında planlı süre ve duruş kapsamı düzeltildi; yeniden işlem çift sayımı önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f73f57b24994aa7"/>
   <x:tableParts count="1">
